--- a/api_testing/casos_api.xlsx
+++ b/api_testing/casos_api.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\OneDrive\Escritorio\QA\ProyectoFinal-BelenFn\api_testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CFB858B-F1B1-4785-8211-F5A90B43DD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB83A7CE-2E12-4591-BD3D-5A6645CD1CD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E80FBC6E-633F-47DA-8889-2FFD4659E969}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Caso Api" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -76,21 +76,6 @@
   </si>
   <si>
     <t>404 o vacío</t>
-  </si>
-  <si>
-    <t>Columna1</t>
-  </si>
-  <si>
-    <t>Columna2</t>
-  </si>
-  <si>
-    <t>Columna3</t>
-  </si>
-  <si>
-    <t>Columna4</t>
-  </si>
-  <si>
-    <t>Columna5</t>
   </si>
 </sst>
 </file>
@@ -198,14 +183,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{877B3D2B-0608-4CC4-9A75-55E8C30D099E}" name="Tabla3" displayName="Tabla3" ref="A2:E6" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A2:E6" xr:uid="{877B3D2B-0608-4CC4-9A75-55E8C30D099E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B2D3BFB9-03E7-4D0A-B015-0422BC08B188}" name="Tabla4" displayName="Tabla4" ref="A2:E5" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A2:E5" xr:uid="{B2D3BFB9-03E7-4D0A-B015-0422BC08B188}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{F232E7E9-D8DD-413B-A537-D44AD21728D2}" name="Columna1" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3D844427-4A9B-4B2C-99C1-6036BA259001}" name="Columna2" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{37C69DF5-675C-4079-A7EE-65CA91D11204}" name="Columna3" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{4C88D0BD-1297-4994-BFBF-680375838AC5}" name="Columna4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{F1203B51-75A3-48BB-B68A-7815F9BF9232}" name="Columna5" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{ACFBCBEA-6F5F-4DF6-A3B3-2ABB46FD66D9}" name="ID" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{DE80169E-DB1A-4810-949B-568E2A8EE567}" name="Método" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{23031B9A-60A0-47C9-9A14-BC73927B4602}" name="Endpoint" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{ABD1E76F-8720-4CA7-BDF9-63F77AD310D0}" name="Resultado Esperado" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{1812B791-18EF-4FBB-88C6-CF4BB6957A45}" name="Estado" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -508,58 +493,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0C1C0D4-DA77-4CE2-93BC-14AE17122F06}">
-  <dimension ref="A2:E6"/>
+  <dimension ref="A2:E5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="11.26953125" customWidth="1"/>
+    <col min="4" max="4" width="19.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
+      <c r="A3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>9</v>
@@ -567,35 +552,18 @@
     </row>
     <row r="5" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
